--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11644,7 +11644,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136183969</v>
       </c>
       <c r="B13" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>136198394</v>
       </c>
       <c r="B14" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136183979</v>
       </c>
       <c r="B16" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>136203732</v>
       </c>
       <c r="B17" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>136183980</v>
       </c>
       <c r="B50" t="n">
-        <v>92446</v>
+        <v>92449</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>135669073</v>
       </c>
       <c r="B56" t="n">
-        <v>100612</v>
+        <v>100615</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>135669652</v>
       </c>
       <c r="B57" t="n">
-        <v>100612</v>
+        <v>100615</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>136179870</v>
       </c>
       <c r="B58" t="n">
-        <v>100612</v>
+        <v>100615</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>136240862</v>
       </c>
       <c r="B59" t="n">
-        <v>100612</v>
+        <v>100615</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>136225509</v>
       </c>
       <c r="B61" t="n">
-        <v>87692</v>
+        <v>87694</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136183946</v>
       </c>
       <c r="B77" t="n">
-        <v>98407</v>
+        <v>98410</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>136198394</v>
       </c>
       <c r="B14" t="n">
-        <v>92922</v>
+        <v>92923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136183979</v>
       </c>
       <c r="B16" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>136203732</v>
       </c>
       <c r="B17" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Alexander Singer, Erica Hästdahl, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6099,7 +6099,7 @@
         <v>136183980</v>
       </c>
       <c r="B50" t="n">
-        <v>92449</v>
+        <v>92450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6814,7 +6814,7 @@
         <v>135669073</v>
       </c>
       <c r="B56" t="n">
-        <v>100615</v>
+        <v>100616</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>135669652</v>
       </c>
       <c r="B57" t="n">
-        <v>100615</v>
+        <v>100616</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>136179870</v>
       </c>
       <c r="B58" t="n">
-        <v>100615</v>
+        <v>100616</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>136240862</v>
       </c>
       <c r="B59" t="n">
-        <v>100615</v>
+        <v>100616</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -9161,7 +9161,7 @@
         <v>136183946</v>
       </c>
       <c r="B77" t="n">
-        <v>98410</v>
+        <v>98411</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11644,7 +11644,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ119"/>
+  <dimension ref="A1:AZ123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Alexander Singer, Erica Hästdahl, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner, Uno Skog, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136227071</v>
+        <v>136183957</v>
       </c>
       <c r="B31" t="n">
         <v>83466</v>
@@ -3940,17 +3940,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännaälven, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440711</v>
+        <v>440579</v>
       </c>
       <c r="R31" t="n">
-        <v>7171132</v>
+        <v>7171056</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4004,24 +4004,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Uno Skog, Cajsa Björkén, Moa Björnberg Dillner, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227071</t>
+          <t>https://artportalen.se/Sighting/136183957</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136240851</v>
+        <v>136227071</v>
       </c>
       <c r="B32" t="n">
         <v>83466</v>
@@ -4049,24 +4049,20 @@
           <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440804</v>
+        <v>440711</v>
       </c>
       <c r="R32" t="n">
-        <v>7171171</v>
+        <v>7171132</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4095,7 +4091,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4105,7 +4101,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4120,24 +4116,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240851</t>
+          <t>https://artportalen.se/Sighting/136227071</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136240854</v>
+        <v>136240851</v>
       </c>
       <c r="B33" t="n">
         <v>83466</v>
@@ -4176,10 +4172,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440664</v>
+        <v>440804</v>
       </c>
       <c r="R33" t="n">
-        <v>7171097</v>
+        <v>7171171</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4211,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4221,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4247,13 +4243,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240854</t>
+          <t>https://artportalen.se/Sighting/136240851</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136240856</v>
+        <v>136240854</v>
       </c>
       <c r="B34" t="n">
         <v>83466</v>
@@ -4292,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440641</v>
+        <v>440664</v>
       </c>
       <c r="R34" t="n">
-        <v>7171102</v>
+        <v>7171097</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4327,7 +4323,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4337,7 +4333,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,54 +4359,58 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240856</t>
+          <t>https://artportalen.se/Sighting/136240854</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135670792</v>
+        <v>136240856</v>
       </c>
       <c r="B35" t="n">
-        <v>75533</v>
+        <v>83466</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1776</v>
+        <v>1467</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brännälven, Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440382</v>
+        <v>440641</v>
       </c>
       <c r="R35" t="n">
-        <v>7171339</v>
+        <v>7171102</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4434,12 +4434,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4459,22 +4469,22 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670792</t>
+          <t>https://artportalen.se/Sighting/136240856</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135671135</v>
+        <v>135670792</v>
       </c>
       <c r="B36" t="n">
-        <v>75557</v>
+        <v>75533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,10 +4516,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440411</v>
+        <v>440382</v>
       </c>
       <c r="R36" t="n">
-        <v>7171343</v>
+        <v>7171339</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4561,19 +4571,19 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135671135</t>
+          <t>https://artportalen.se/Sighting/135670792</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136179832</v>
+        <v>135671135</v>
       </c>
       <c r="B37" t="n">
         <v>75557</v>
@@ -4604,17 +4614,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Brännälven, Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440778</v>
+        <v>440411</v>
       </c>
       <c r="R37" t="n">
-        <v>7171278</v>
+        <v>7171343</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4638,22 +4648,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4668,24 +4668,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Erica Hästdahl, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179832</t>
+          <t>https://artportalen.se/Sighting/135671135</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136179864</v>
+        <v>136179832</v>
       </c>
       <c r="B38" t="n">
         <v>75557</v>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440515</v>
+        <v>440778</v>
       </c>
       <c r="R38" t="n">
-        <v>7171058</v>
+        <v>7171278</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4791,13 +4791,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179864</t>
+          <t>https://artportalen.se/Sighting/136179832</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136179866</v>
+        <v>136179864</v>
       </c>
       <c r="B39" t="n">
         <v>75557</v>
@@ -4832,13 +4832,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440506</v>
+        <v>440515</v>
       </c>
       <c r="R39" t="n">
-        <v>7171048</v>
+        <v>7171058</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4903,13 +4903,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179866</t>
+          <t>https://artportalen.se/Sighting/136179864</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136179873</v>
+        <v>136179866</v>
       </c>
       <c r="B40" t="n">
         <v>75557</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440502</v>
+        <v>440506</v>
       </c>
       <c r="R40" t="n">
-        <v>7171059</v>
+        <v>7171048</v>
       </c>
       <c r="S40" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5009,19 +5009,19 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179873</t>
+          <t>https://artportalen.se/Sighting/136179866</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136179874</v>
+        <v>136179873</v>
       </c>
       <c r="B41" t="n">
         <v>75557</v>
@@ -5056,13 +5056,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440479</v>
+        <v>440502</v>
       </c>
       <c r="R41" t="n">
-        <v>7171050</v>
+        <v>7171059</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5121,19 +5121,19 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179874</t>
+          <t>https://artportalen.se/Sighting/136179873</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136219638</v>
+        <v>136179874</v>
       </c>
       <c r="B42" t="n">
         <v>75557</v>
@@ -5162,22 +5162,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440319</v>
+        <v>440479</v>
       </c>
       <c r="R42" t="n">
-        <v>7171567</v>
+        <v>7171050</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5201,12 +5198,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5215,46 +5222,30 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136219638</t>
+          <t>https://artportalen.se/Sighting/136179874</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136219642</v>
+        <v>136219638</v>
       </c>
       <c r="B43" t="n">
         <v>75557</v>
@@ -5292,10 +5283,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440288</v>
+        <v>440319</v>
       </c>
       <c r="R43" t="n">
-        <v>7171571</v>
+        <v>7171567</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5369,13 +5360,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136219642</t>
+          <t>https://artportalen.se/Sighting/136219638</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136219649</v>
+        <v>136219642</v>
       </c>
       <c r="B44" t="n">
         <v>75557</v>
@@ -5413,10 +5404,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440265</v>
+        <v>440288</v>
       </c>
       <c r="R44" t="n">
-        <v>7171589</v>
+        <v>7171571</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5490,13 +5481,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136219649</t>
+          <t>https://artportalen.se/Sighting/136219642</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136227067</v>
+        <v>136219649</v>
       </c>
       <c r="B45" t="n">
         <v>75557</v>
@@ -5525,19 +5516,22 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440804</v>
+        <v>440265</v>
       </c>
       <c r="R45" t="n">
-        <v>7171161</v>
+        <v>7171589</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5561,22 +5555,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5585,30 +5569,46 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227067</t>
+          <t>https://artportalen.se/Sighting/136219649</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136240852</v>
+        <v>136227067</v>
       </c>
       <c r="B46" t="n">
         <v>75557</v>
@@ -5636,24 +5636,20 @@
           <t>Egea &amp; Torrente</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440807</v>
+        <v>440804</v>
       </c>
       <c r="R46" t="n">
-        <v>7171171</v>
+        <v>7171161</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5682,7 +5678,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5692,7 +5688,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5707,24 +5703,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240852</t>
+          <t>https://artportalen.se/Sighting/136227067</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136240863</v>
+        <v>136240852</v>
       </c>
       <c r="B47" t="n">
         <v>75557</v>
@@ -5763,13 +5759,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440432</v>
+        <v>440807</v>
       </c>
       <c r="R47" t="n">
-        <v>7171004</v>
+        <v>7171171</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5798,7 +5794,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5808,7 +5804,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5834,13 +5830,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240863</t>
+          <t>https://artportalen.se/Sighting/136240852</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136240866</v>
+        <v>136240863</v>
       </c>
       <c r="B48" t="n">
         <v>75557</v>
@@ -5879,13 +5875,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440410</v>
+        <v>440432</v>
       </c>
       <c r="R48" t="n">
-        <v>7171005</v>
+        <v>7171004</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5914,7 +5910,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5920,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,54 +5946,55 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240866</t>
+          <t>https://artportalen.se/Sighting/136240863</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136179859</v>
+        <v>136240866</v>
       </c>
       <c r="B49" t="n">
-        <v>80353</v>
+        <v>75557</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1813</v>
+        <v>1776</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ros-skivlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lecidea roseotincta</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Coppins &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>Egea &amp; Torrente</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440540</v>
+        <v>440410</v>
       </c>
       <c r="R49" t="n">
-        <v>7171050</v>
+        <v>7171005</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6029,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6039,12 +6036,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Två små bålar på slät bark av gråal, ca 30 cm i diameter. Sporer mestadels encelliga, med midja, 11-12x6-7 um, bruna som äldre. Bål K+ magenta. Inga asci funna. Fyndet ska sekvenseras.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6053,75 +6045,55 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gråal</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Alnus incana</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Alnus incana</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179859</t>
+          <t>https://artportalen.se/Sighting/136240866</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136183980</v>
+        <v>136179859</v>
       </c>
       <c r="B50" t="n">
-        <v>92450</v>
+        <v>80353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2063</v>
+        <v>1813</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ros-skivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lecidea roseotincta</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Coppins &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6130,17 +6102,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännaälven, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440386</v>
+        <v>440540</v>
       </c>
       <c r="R50" t="n">
-        <v>7171173</v>
+        <v>7171050</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6169,7 +6141,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6179,12 +6151,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På död granticka på granlåga över en liten bäck.</t>
+          <t>Två små bålar på slät bark av gråal, ca 30 cm i diameter. Sporer mestadels encelliga, med midja, 11-12x6-7 um, bruna som äldre. Bål K+ magenta. Inga asci funna. Fyndet ska sekvenseras.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6193,87 +6165,94 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>tajgagranticka</t>
+          <t>gråal</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Porodaedalea abietis</t>
+          <t>Alnus incana</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Porodaedalea abietis</t>
+          <t>Alnus incana</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136183980</t>
+          <t>https://artportalen.se/Sighting/136179859</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>94765680</v>
+        <v>136183980</v>
       </c>
       <c r="B51" t="n">
-        <v>80433</v>
+        <v>92450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännaälven, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441117</v>
+        <v>440386</v>
       </c>
       <c r="R51" t="n">
-        <v>7171376</v>
+        <v>7171173</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6297,17 +6276,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>På död granticka på granlåga över en liten bäck.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6316,35 +6305,46 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tajgagranticka</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Porodaedalea abietis</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Porodaedalea abietis</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765680</t>
+          <t>https://artportalen.se/Sighting/136183980</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126010917</v>
+        <v>94765680</v>
       </c>
       <c r="B52" t="n">
         <v>80433</v>
@@ -6373,22 +6373,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440756</v>
+        <v>441117</v>
       </c>
       <c r="R52" t="n">
-        <v>7171142</v>
+        <v>7171376</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6412,12 +6409,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6426,39 +6428,38 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126010917</t>
+          <t>https://artportalen.se/Sighting/94765680</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136179834</v>
+        <v>126010917</v>
       </c>
       <c r="B53" t="n">
-        <v>80590</v>
+        <v>80433</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6484,19 +6485,22 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440810</v>
+        <v>440756</v>
       </c>
       <c r="R53" t="n">
-        <v>7171208</v>
+        <v>7171142</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6520,22 +6524,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6544,30 +6538,36 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179834</t>
+          <t>https://artportalen.se/Sighting/126010917</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136179862</v>
+        <v>136179834</v>
       </c>
       <c r="B54" t="n">
         <v>80590</v>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440533</v>
+        <v>440810</v>
       </c>
       <c r="R54" t="n">
-        <v>7171050</v>
+        <v>7171208</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6647,12 +6647,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6663,21 +6658,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6693,13 +6673,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179862</t>
+          <t>https://artportalen.se/Sighting/136179834</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136227069</v>
+        <v>136179862</v>
       </c>
       <c r="B55" t="n">
         <v>80590</v>
@@ -6730,17 +6710,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440727</v>
+        <v>440533</v>
       </c>
       <c r="R55" t="n">
-        <v>7171129</v>
+        <v>7171050</v>
       </c>
       <c r="S55" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6769,7 +6749,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6779,7 +6759,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6790,69 +6775,84 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227069</t>
+          <t>https://artportalen.se/Sighting/136179862</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135669073</v>
+        <v>136227069</v>
       </c>
       <c r="B56" t="n">
-        <v>100616</v>
+        <v>80590</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brännälven, Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440336</v>
+        <v>440727</v>
       </c>
       <c r="R56" t="n">
-        <v>7171504</v>
+        <v>7171129</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6876,12 +6876,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6896,24 +6906,24 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669073</t>
+          <t>https://artportalen.se/Sighting/136227069</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135669652</v>
+        <v>135669073</v>
       </c>
       <c r="B57" t="n">
         <v>100616</v>
@@ -6948,10 +6958,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440305</v>
+        <v>440336</v>
       </c>
       <c r="R57" t="n">
-        <v>7171406</v>
+        <v>7171504</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7009,13 +7019,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669652</t>
+          <t>https://artportalen.se/Sighting/135669073</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136179870</v>
+        <v>135669652</v>
       </c>
       <c r="B58" t="n">
         <v>100616</v>
@@ -7046,17 +7056,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Brännälven, Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440517</v>
+        <v>440305</v>
       </c>
       <c r="R58" t="n">
-        <v>7171043</v>
+        <v>7171406</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7080,22 +7090,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7110,24 +7110,24 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Erica Hästdahl, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179870</t>
+          <t>https://artportalen.se/Sighting/135669652</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136240862</v>
+        <v>136179870</v>
       </c>
       <c r="B59" t="n">
         <v>100616</v>
@@ -7155,21 +7155,17 @@
           <t>(Laest.) Fr.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440482</v>
+        <v>440517</v>
       </c>
       <c r="R59" t="n">
-        <v>7171033</v>
+        <v>7171043</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7201,7 +7197,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7211,7 +7207,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7226,27 +7222,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240862</t>
+          <t>https://artportalen.se/Sighting/136179870</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>94765677</v>
+        <v>136240862</v>
       </c>
       <c r="B60" t="n">
-        <v>92632</v>
+        <v>100616</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7254,37 +7250,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>2082</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441069</v>
+        <v>440482</v>
       </c>
       <c r="R60" t="n">
-        <v>7171351</v>
+        <v>7171033</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7308,12 +7308,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7324,78 +7334,69 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765677</t>
+          <t>https://artportalen.se/Sighting/136240862</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136225509</v>
+        <v>94765677</v>
       </c>
       <c r="B61" t="n">
-        <v>87694</v>
+        <v>92632</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3606</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tvådoftspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius diosmus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kühner</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bränna, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440408</v>
+        <v>441069</v>
       </c>
       <c r="R61" t="n">
-        <v>7170989</v>
+        <v>7171351</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7419,22 +7420,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7445,31 +7436,36 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Cajsa Björkén, Uno Skog, Rashid Kadhim, Moa Björnberg Dillner, Alexander Singer</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136225509</t>
+          <t>https://artportalen.se/Sighting/94765677</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>94765698</v>
+        <v>136225509</v>
       </c>
       <c r="B62" t="n">
-        <v>79327</v>
+        <v>87694</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7477,37 +7473,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>3606</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvådoftspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius diosmus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Bränna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441253</v>
+        <v>440408</v>
       </c>
       <c r="R62" t="n">
-        <v>7171528</v>
+        <v>7170989</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7531,12 +7531,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7547,58 +7557,53 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Erica Hästdahl, Cajsa Björkén, Uno Skog, Rashid Kadhim, Moa Björnberg Dillner, Alexander Singer</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765698</t>
+          <t>https://artportalen.se/Sighting/136225509</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>94765676</v>
+        <v>94765698</v>
       </c>
       <c r="B63" t="n">
-        <v>75300</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7608,10 +7613,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441052</v>
+        <v>441253</v>
       </c>
       <c r="R63" t="n">
-        <v>7171282</v>
+        <v>7171528</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7657,7 +7662,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Gråal</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7674,54 +7679,54 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765676</t>
+          <t>https://artportalen.se/Sighting/94765698</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>94765697</v>
+        <v>136183970</v>
       </c>
       <c r="B64" t="n">
-        <v>83307</v>
+        <v>79474</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännaälven, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441253</v>
+        <v>440607</v>
       </c>
       <c r="R64" t="n">
-        <v>7171528</v>
+        <v>7171156</v>
       </c>
       <c r="S64" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7745,12 +7750,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7761,36 +7776,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765697</t>
+          <t>https://artportalen.se/Sighting/136183970</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136179861</v>
+        <v>94765676</v>
       </c>
       <c r="B65" t="n">
-        <v>78832</v>
+        <v>75300</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7798,37 +7808,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6443</v>
+        <v>6428</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440533</v>
+        <v>441052</v>
       </c>
       <c r="R65" t="n">
-        <v>7171050</v>
+        <v>7171282</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7852,27 +7862,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Utsn bål På grankvist</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7883,31 +7878,36 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Gråal</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179861</t>
+          <t>https://artportalen.se/Sighting/94765676</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>94765681</v>
+        <v>94765697</v>
       </c>
       <c r="B66" t="n">
-        <v>80432</v>
+        <v>83307</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7915,21 +7915,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441117</v>
+        <v>441253</v>
       </c>
       <c r="R66" t="n">
-        <v>7171376</v>
+        <v>7171528</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7977,11 +7977,6 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7993,7 +7988,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8010,38 +8005,38 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765681</t>
+          <t>https://artportalen.se/Sighting/94765697</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136179833</v>
+        <v>136179861</v>
       </c>
       <c r="B67" t="n">
-        <v>80589</v>
+        <v>78832</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6443</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8051,13 +8046,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440810</v>
+        <v>440533</v>
       </c>
       <c r="R67" t="n">
-        <v>7171208</v>
+        <v>7171050</v>
       </c>
       <c r="S67" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8086,7 +8081,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8096,7 +8091,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Utsn bål På grankvist</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8122,16 +8122,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179833</t>
+          <t>https://artportalen.se/Sighting/136179861</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136227075</v>
+        <v>94765681</v>
       </c>
       <c r="B68" t="n">
-        <v>80589</v>
+        <v>80432</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8163,13 +8163,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440666</v>
+        <v>441117</v>
       </c>
       <c r="R68" t="n">
-        <v>7171110</v>
+        <v>7171376</v>
       </c>
       <c r="S68" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8193,22 +8193,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8219,69 +8214,74 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227075</t>
+          <t>https://artportalen.se/Sighting/94765681</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>94765678</v>
+        <v>136179833</v>
       </c>
       <c r="B69" t="n">
-        <v>79583</v>
+        <v>80589</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441069</v>
+        <v>440810</v>
       </c>
       <c r="R69" t="n">
-        <v>7171351</v>
+        <v>7171208</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8305,12 +8305,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8321,58 +8331,53 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765678</t>
+          <t>https://artportalen.se/Sighting/136179833</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>94765682</v>
+        <v>136227075</v>
       </c>
       <c r="B70" t="n">
-        <v>80461</v>
+        <v>80589</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8382,13 +8387,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441117</v>
+        <v>440666</v>
       </c>
       <c r="R70" t="n">
-        <v>7171376</v>
+        <v>7171110</v>
       </c>
       <c r="S70" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8412,17 +8417,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt förekommande i dalgången</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8433,36 +8443,31 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765682</t>
+          <t>https://artportalen.se/Sighting/136227075</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136219658</v>
+        <v>94765678</v>
       </c>
       <c r="B71" t="n">
-        <v>80594</v>
+        <v>79583</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8470,40 +8475,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440288</v>
+        <v>441069</v>
       </c>
       <c r="R71" t="n">
-        <v>7171585</v>
+        <v>7171351</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8527,12 +8529,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8541,49 +8543,38 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136219658</t>
+          <t>https://artportalen.se/Sighting/94765678</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>94765683</v>
+        <v>94765682</v>
       </c>
       <c r="B72" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8591,21 +8582,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8686,63 +8677,57 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765683</t>
+          <t>https://artportalen.se/Sighting/94765682</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136183976</v>
+        <v>136219658</v>
       </c>
       <c r="B73" t="n">
-        <v>58006</v>
+        <v>80594</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Brännaälven, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440525</v>
+        <v>440288</v>
       </c>
       <c r="R73" t="n">
-        <v>7171145</v>
+        <v>7171585</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8766,27 +8751,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:29</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Hackar i flera döda eller toppbrutna granar. Hona</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8795,76 +8765,87 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136183976</t>
+          <t>https://artportalen.se/Sighting/136219658</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136227091</v>
+        <v>94765683</v>
       </c>
       <c r="B74" t="n">
-        <v>58006</v>
+        <v>80467</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440537</v>
+        <v>441117</v>
       </c>
       <c r="R74" t="n">
-        <v>7171124</v>
+        <v>7171376</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8888,27 +8869,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt förekommande i dalgången</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8919,31 +8890,36 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227091</t>
+          <t>https://artportalen.se/Sighting/94765683</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136183983</v>
+        <v>136183976</v>
       </c>
       <c r="B75" t="n">
-        <v>58110</v>
+        <v>58006</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8951,16 +8927,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8973,19 +8949,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Brännaälven, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440379</v>
+        <v>440525</v>
       </c>
       <c r="R75" t="n">
-        <v>7171179</v>
+        <v>7171145</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9014,7 +8995,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9024,7 +9005,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Hackar i flera döda eller toppbrutna granar. Hona</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9050,54 +9036,59 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136183983</t>
+          <t>https://artportalen.se/Sighting/136183976</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>94765684</v>
+        <v>136227091</v>
       </c>
       <c r="B76" t="n">
-        <v>99456</v>
+        <v>58006</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441163</v>
+        <v>440537</v>
       </c>
       <c r="R76" t="n">
-        <v>7171428</v>
+        <v>7171124</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9121,12 +9112,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9141,65 +9147,69 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765684</t>
+          <t>https://artportalen.se/Sighting/136227091</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136183946</v>
+        <v>136183983</v>
       </c>
       <c r="B77" t="n">
-        <v>98411</v>
+        <v>58110</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220250</v>
+        <v>103031</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Brännaälven, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440754</v>
+        <v>440379</v>
       </c>
       <c r="R77" t="n">
-        <v>7171146</v>
+        <v>7171179</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9228,7 +9238,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9238,7 +9248,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9264,38 +9274,38 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136183946</t>
+          <t>https://artportalen.se/Sighting/136183983</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136183974</v>
+        <v>136183958</v>
       </c>
       <c r="B78" t="n">
-        <v>78483</v>
+        <v>100968</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>219851</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Hässlebrodd</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Milium effusum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9305,13 +9315,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440550</v>
+        <v>440559</v>
       </c>
       <c r="R78" t="n">
-        <v>7171146</v>
+        <v>7171053</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9340,7 +9350,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9350,7 +9360,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9370,63 +9380,60 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Cajsa Björkén, Moa Björnberg Dillner, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136183974</t>
+          <t>https://artportalen.se/Sighting/136183958</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136227078</v>
+        <v>94765684</v>
       </c>
       <c r="B79" t="n">
-        <v>85400</v>
+        <v>99456</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229431</v>
+        <v>219880</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglavshårprick</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Niesslia lobariae</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Etayo &amp; Diederich</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440608</v>
+        <v>441163</v>
       </c>
       <c r="R79" t="n">
-        <v>7171089</v>
+        <v>7171428</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9450,27 +9457,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Hittades under mykologiveckan 2026. Bekräftad av Cajsa Björken och Robin Isaksson.</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9479,34 +9471,33 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227078</t>
+          <t>https://artportalen.se/Sighting/94765684</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>94765671</v>
+        <v>136183946</v>
       </c>
       <c r="B80" t="n">
-        <v>80392</v>
+        <v>98411</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9514,37 +9505,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>220250</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440823</v>
+        <v>440754</v>
       </c>
       <c r="R80" t="n">
-        <v>7171152</v>
+        <v>7171146</v>
       </c>
       <c r="S80" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9568,12 +9559,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9584,74 +9585,69 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Gråal</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765671</t>
+          <t>https://artportalen.se/Sighting/136183946</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136179840</v>
+        <v>136183974</v>
       </c>
       <c r="B81" t="n">
-        <v>80539</v>
+        <v>78483</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229497</v>
+        <v>228579</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Brännaälven, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440739</v>
+        <v>440550</v>
       </c>
       <c r="R81" t="n">
-        <v>7171136</v>
+        <v>7171146</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9680,7 +9676,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9690,7 +9686,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9705,69 +9701,68 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179840</t>
+          <t>https://artportalen.se/Sighting/136183974</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136240864</v>
+        <v>136227078</v>
       </c>
       <c r="B82" t="n">
-        <v>80609</v>
+        <v>85400</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229504</v>
+        <v>229431</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lunglavshårprick</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Niesslia lobariae</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Etayo &amp; Diederich</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440420</v>
+        <v>440608</v>
       </c>
       <c r="R82" t="n">
-        <v>7170992</v>
+        <v>7171089</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9796,7 +9791,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9806,7 +9801,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Hittades under mykologiveckan 2026. Bekräftad av Cajsa Björken och Robin Isaksson.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9815,55 +9815,56 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240864</t>
+          <t>https://artportalen.se/Sighting/136227078</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>94765675</v>
+        <v>94765671</v>
       </c>
       <c r="B83" t="n">
-        <v>79043</v>
+        <v>80392</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229615</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grynig kolvlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pilophorus cereolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9873,10 +9874,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440921</v>
+        <v>440823</v>
       </c>
       <c r="R83" t="n">
-        <v>7171254</v>
+        <v>7171152</v>
       </c>
       <c r="S83" t="n">
         <v>50</v>
@@ -9911,11 +9912,6 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På fuktiga klippor invid vattendraget</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9924,6 +9920,11 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Gråal</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9939,38 +9940,38 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94765675</t>
+          <t>https://artportalen.se/Sighting/94765671</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136179844</v>
+        <v>136179840</v>
       </c>
       <c r="B84" t="n">
-        <v>75488</v>
+        <v>80539</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229651</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9980,13 +9981,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440655</v>
+        <v>440739</v>
       </c>
       <c r="R84" t="n">
-        <v>7171078</v>
+        <v>7171136</v>
       </c>
       <c r="S84" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10015,7 +10016,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10025,7 +10026,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10051,51 +10052,55 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179844</t>
+          <t>https://artportalen.se/Sighting/136179840</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136198395</v>
+        <v>136240864</v>
       </c>
       <c r="B85" t="n">
-        <v>75488</v>
+        <v>80609</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229651</v>
+        <v>229504</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440586</v>
+        <v>440420</v>
       </c>
       <c r="R85" t="n">
-        <v>7171052</v>
+        <v>7170992</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10125,11 +10130,21 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10139,83 +10154,68 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr"/>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136198395</t>
+          <t>https://artportalen.se/Sighting/136240864</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136203727</v>
+        <v>94765675</v>
       </c>
       <c r="B86" t="n">
-        <v>75488</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229651</v>
+        <v>229615</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Grynig kolvlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Pilophorus cereolus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440702</v>
+        <v>440921</v>
       </c>
       <c r="R86" t="n">
-        <v>7171122</v>
+        <v>7171254</v>
       </c>
       <c r="S86" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10239,22 +10239,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>10:25</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>10:25</t>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På fuktiga klippor invid vattendraget</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10269,24 +10264,24 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Ola Hammarström, Fredrik Larsson, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136203727</t>
+          <t>https://artportalen.se/Sighting/94765675</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136227076</v>
+        <v>136179844</v>
       </c>
       <c r="B87" t="n">
         <v>75488</v>
@@ -10317,17 +10312,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440666</v>
+        <v>440655</v>
       </c>
       <c r="R87" t="n">
-        <v>7171110</v>
+        <v>7171078</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10356,7 +10351,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10366,7 +10361,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10381,24 +10376,24 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227076</t>
+          <t>https://artportalen.se/Sighting/136179844</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>136227082</v>
+        <v>136183956</v>
       </c>
       <c r="B88" t="n">
         <v>75488</v>
@@ -10433,13 +10428,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440586</v>
+        <v>440598</v>
       </c>
       <c r="R88" t="n">
-        <v>7171082</v>
+        <v>7171050</v>
       </c>
       <c r="S88" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10468,7 +10463,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10478,7 +10473,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Foton. På gråal.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10489,28 +10489,43 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Uno Skog, Cajsa Björkén, Moa Björnberg Dillner, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227082</t>
+          <t>https://artportalen.se/Sighting/136183956</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136227084</v>
+        <v>136198395</v>
       </c>
       <c r="B89" t="n">
         <v>75488</v>
@@ -10545,13 +10560,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440572</v>
+        <v>440586</v>
       </c>
       <c r="R89" t="n">
-        <v>7171049</v>
+        <v>7171052</v>
       </c>
       <c r="S89" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10578,21 +10593,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10602,27 +10607,42 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr"/>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227084</t>
+          <t>https://artportalen.se/Sighting/136198395</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>136227086</v>
+        <v>136203727</v>
       </c>
       <c r="B90" t="n">
         <v>75488</v>
@@ -10653,17 +10673,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440574</v>
+        <v>440702</v>
       </c>
       <c r="R90" t="n">
-        <v>7171074</v>
+        <v>7171122</v>
       </c>
       <c r="S90" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10692,7 +10712,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10702,7 +10722,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10717,24 +10737,24 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227086</t>
+          <t>https://artportalen.se/Sighting/136203727</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>136240855</v>
+        <v>136227076</v>
       </c>
       <c r="B91" t="n">
         <v>75488</v>
@@ -10762,24 +10782,20 @@
           <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440667</v>
+        <v>440666</v>
       </c>
       <c r="R91" t="n">
-        <v>7171108</v>
+        <v>7171110</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10808,7 +10824,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10818,7 +10834,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10833,24 +10849,24 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240855</t>
+          <t>https://artportalen.se/Sighting/136227076</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>136240860</v>
+        <v>136227082</v>
       </c>
       <c r="B92" t="n">
         <v>75488</v>
@@ -10878,24 +10894,20 @@
           <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440592</v>
+        <v>440586</v>
       </c>
       <c r="R92" t="n">
-        <v>7171056</v>
+        <v>7171082</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10924,7 +10936,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10934,7 +10946,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10949,65 +10961,65 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240860</t>
+          <t>https://artportalen.se/Sighting/136227082</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>136179845</v>
+        <v>136227084</v>
       </c>
       <c r="B93" t="n">
-        <v>75490</v>
+        <v>75488</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229653</v>
+        <v>229651</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440666</v>
+        <v>440572</v>
       </c>
       <c r="R93" t="n">
-        <v>7171114</v>
+        <v>7171049</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11036,7 +11048,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11046,12 +11058,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11066,65 +11073,65 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179845</t>
+          <t>https://artportalen.se/Sighting/136227084</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>136179846</v>
+        <v>136227086</v>
       </c>
       <c r="B94" t="n">
-        <v>75490</v>
+        <v>75488</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229653</v>
+        <v>229651</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440664</v>
+        <v>440574</v>
       </c>
       <c r="R94" t="n">
-        <v>7171110</v>
+        <v>7171074</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11153,7 +11160,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11163,12 +11170,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11183,68 +11185,69 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179846</t>
+          <t>https://artportalen.se/Sighting/136227086</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112136732</v>
+        <v>136240855</v>
       </c>
       <c r="B95" t="n">
-        <v>75356</v>
+        <v>75488</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229654</v>
+        <v>229651</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Sommerf.) D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Styggdalen, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>441122</v>
+        <v>440667</v>
       </c>
       <c r="R95" t="n">
-        <v>7171213</v>
+        <v>7171108</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11268,12 +11271,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11282,75 +11295,75 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112136732</t>
+          <t>https://artportalen.se/Sighting/136240855</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126010915</v>
+        <v>136240860</v>
       </c>
       <c r="B96" t="n">
-        <v>75356</v>
+        <v>75488</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229654</v>
+        <v>229651</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>(Sommerf.) D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440756</v>
+        <v>440592</v>
       </c>
       <c r="R96" t="n">
-        <v>7171142</v>
+        <v>7171056</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11374,12 +11387,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11388,54 +11411,33 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>skrovellav</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126010915</t>
+          <t>https://artportalen.se/Sighting/136240860</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>136179837</v>
+        <v>136179845</v>
       </c>
       <c r="B97" t="n">
-        <v>75492</v>
+        <v>75490</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11443,21 +11445,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229654</v>
+        <v>229653</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11467,10 +11469,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440777</v>
+        <v>440666</v>
       </c>
       <c r="R97" t="n">
-        <v>7171141</v>
+        <v>7171114</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11502,7 +11504,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11512,7 +11514,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11532,22 +11539,22 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179837</t>
+          <t>https://artportalen.se/Sighting/136179845</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>136179841</v>
+        <v>136179846</v>
       </c>
       <c r="B98" t="n">
-        <v>75492</v>
+        <v>75490</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11555,21 +11562,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229654</v>
+        <v>229653</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11579,10 +11586,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440725</v>
+        <v>440664</v>
       </c>
       <c r="R98" t="n">
-        <v>7171132</v>
+        <v>7171110</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11614,7 +11621,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11624,7 +11631,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11650,16 +11662,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179841</t>
+          <t>https://artportalen.se/Sighting/136179846</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>136179851</v>
+        <v>112136732</v>
       </c>
       <c r="B99" t="n">
-        <v>75492</v>
+        <v>75356</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11685,19 +11697,22 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440592</v>
+        <v>441122</v>
       </c>
       <c r="R99" t="n">
-        <v>7171068</v>
+        <v>7171213</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11721,22 +11736,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11745,33 +11750,34 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179851</t>
+          <t>https://artportalen.se/Sighting/112136732</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>136179857</v>
+        <v>126010915</v>
       </c>
       <c r="B100" t="n">
-        <v>75492</v>
+        <v>75356</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11797,19 +11803,22 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Gråalskog vid Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440594</v>
+        <v>440756</v>
       </c>
       <c r="R100" t="n">
-        <v>7171044</v>
+        <v>7171142</v>
       </c>
       <c r="S100" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11833,22 +11842,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:13</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:13</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11857,30 +11856,51 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Frodig och gamma gråalskog i brant terräng, på lerskiffer.</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>skrovellav</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Uno Skog, Moa Björnberg Dillner, Rashid Kadhim, Alexander Singer, Erica Hästdahl</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179857</t>
+          <t>https://artportalen.se/Sighting/126010915</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>136203725</v>
+        <v>136179837</v>
       </c>
       <c r="B101" t="n">
         <v>75492</v>
@@ -11915,13 +11935,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440726</v>
+        <v>440777</v>
       </c>
       <c r="R101" t="n">
-        <v>7171111</v>
+        <v>7171141</v>
       </c>
       <c r="S101" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11950,7 +11970,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11960,7 +11980,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11975,24 +11995,24 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136203725</t>
+          <t>https://artportalen.se/Sighting/136179837</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>136227070</v>
+        <v>136179841</v>
       </c>
       <c r="B102" t="n">
         <v>75492</v>
@@ -12023,17 +12043,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440727</v>
+        <v>440725</v>
       </c>
       <c r="R102" t="n">
-        <v>7171129</v>
+        <v>7171132</v>
       </c>
       <c r="S102" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12062,7 +12082,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12072,7 +12092,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12087,24 +12107,24 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227070</t>
+          <t>https://artportalen.se/Sighting/136179841</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>136227073</v>
+        <v>136179851</v>
       </c>
       <c r="B103" t="n">
         <v>75492</v>
@@ -12135,14 +12155,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440733</v>
+        <v>440592</v>
       </c>
       <c r="R103" t="n">
-        <v>7171119</v>
+        <v>7171068</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12174,7 +12194,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12184,7 +12204,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12199,24 +12219,24 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227073</t>
+          <t>https://artportalen.se/Sighting/136179851</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>136240853</v>
+        <v>136179857</v>
       </c>
       <c r="B104" t="n">
         <v>75492</v>
@@ -12244,24 +12264,20 @@
           <t>Diederich &amp; Etayo</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440748</v>
+        <v>440594</v>
       </c>
       <c r="R104" t="n">
-        <v>7171145</v>
+        <v>7171044</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12290,7 +12306,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12300,7 +12316,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12315,24 +12331,24 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240853</t>
+          <t>https://artportalen.se/Sighting/136179857</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>136240858</v>
+        <v>136203725</v>
       </c>
       <c r="B105" t="n">
         <v>75492</v>
@@ -12360,24 +12376,20 @@
           <t>Diederich &amp; Etayo</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440669</v>
+        <v>440726</v>
       </c>
       <c r="R105" t="n">
-        <v>7171116</v>
+        <v>7171111</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12406,7 +12418,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12416,7 +12428,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12431,65 +12443,65 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240858</t>
+          <t>https://artportalen.se/Sighting/136203725</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>136179843</v>
+        <v>136227070</v>
       </c>
       <c r="B106" t="n">
-        <v>80545</v>
+        <v>75492</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229748</v>
+        <v>229654</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440745</v>
+        <v>440727</v>
       </c>
       <c r="R106" t="n">
-        <v>7171143</v>
+        <v>7171129</v>
       </c>
       <c r="S106" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12518,7 +12530,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12528,7 +12540,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12543,68 +12555,65 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179843</t>
+          <t>https://artportalen.se/Sighting/136227070</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>136219661</v>
+        <v>136227073</v>
       </c>
       <c r="B107" t="n">
-        <v>80545</v>
+        <v>75492</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229748</v>
+        <v>229654</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440288</v>
+        <v>440733</v>
       </c>
       <c r="R107" t="n">
-        <v>7171585</v>
+        <v>7171119</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12628,12 +12637,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12642,85 +12661,75 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136219661</t>
+          <t>https://artportalen.se/Sighting/136227073</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>136219654</v>
+        <v>136240853</v>
       </c>
       <c r="B108" t="n">
-        <v>79946</v>
+        <v>75492</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6038705</v>
+        <v>229654</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>440265</v>
+        <v>440748</v>
       </c>
       <c r="R108" t="n">
-        <v>7171589</v>
+        <v>7171145</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12744,12 +12753,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12758,82 +12777,75 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136219654</t>
+          <t>https://artportalen.se/Sighting/136240853</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>136227089</v>
+        <v>136240858</v>
       </c>
       <c r="B109" t="n">
-        <v>79946</v>
+        <v>75492</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6038705</v>
+        <v>229654</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>Diederich &amp; Etayo</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>440530</v>
+        <v>440669</v>
       </c>
       <c r="R109" t="n">
-        <v>7171050</v>
+        <v>7171116</v>
       </c>
       <c r="S109" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12862,7 +12874,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12872,12 +12884,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På grankvist</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12886,71 +12893,71 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227089</t>
+          <t>https://artportalen.se/Sighting/136240858</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>136240859</v>
+        <v>136179843</v>
       </c>
       <c r="B110" t="n">
-        <v>79946</v>
+        <v>80545</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6038705</v>
+        <v>229748</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>440611</v>
+        <v>440745</v>
       </c>
       <c r="R110" t="n">
-        <v>7171084</v>
+        <v>7171143</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12979,7 +12986,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12989,7 +12996,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13004,60 +13011,68 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240859</t>
+          <t>https://artportalen.se/Sighting/136179843</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>136179850</v>
+        <v>136219661</v>
       </c>
       <c r="B111" t="n">
-        <v>85481</v>
+        <v>80545</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6331313</v>
+        <v>229748</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Roselliniella nephromatis</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440611</v>
+        <v>440288</v>
       </c>
       <c r="R111" t="n">
-        <v>7171084</v>
+        <v>7171585</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13081,27 +13096,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13114,63 +13114,81 @@
       <c r="AG111" t="b">
         <v>0</v>
       </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179850</t>
+          <t>https://artportalen.se/Sighting/136219661</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>136179852</v>
+        <v>136219654</v>
       </c>
       <c r="B112" t="n">
-        <v>85481</v>
+        <v>79946</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6331313</v>
+        <v>6038705</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Roselliniella nephromatis</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+          <t>Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440592</v>
+        <v>440265</v>
       </c>
       <c r="R112" t="n">
-        <v>7171068</v>
+        <v>7171589</v>
       </c>
       <c r="S112" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13194,22 +13212,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13222,63 +13230,78 @@
       <c r="AG112" t="b">
         <v>0</v>
       </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179852</t>
+          <t>https://artportalen.se/Sighting/136219654</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>136179854</v>
+        <v>136227089</v>
       </c>
       <c r="B113" t="n">
-        <v>85481</v>
+        <v>79946</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6331313</v>
+        <v>6038705</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Roselliniella nephromatis</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+          <t>Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Brännälven, Jmt</t>
+          <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440616</v>
+        <v>440530</v>
       </c>
       <c r="R113" t="n">
-        <v>7171059</v>
+        <v>7171050</v>
       </c>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13307,7 +13330,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13317,7 +13340,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>På grankvist</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13333,60 +13361,64 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136179854</t>
+          <t>https://artportalen.se/Sighting/136227089</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>136202366</v>
+        <v>136240859</v>
       </c>
       <c r="B114" t="n">
-        <v>85481</v>
+        <v>79946</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6331313</v>
+        <v>6038705</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Roselliniella nephromatis</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440594</v>
+        <v>440611</v>
       </c>
       <c r="R114" t="n">
-        <v>7171053</v>
+        <v>7171084</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13410,12 +13442,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13427,32 +13469,27 @@
       <c r="AG114" t="b">
         <v>0</v>
       </c>
-      <c r="AR114" t="inlineStr"/>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl, Rashid Kadhim, Cajsa Björkén, Alexander Singer, Uno Skog, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136202366</t>
+          <t>https://artportalen.se/Sighting/136240859</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>136227080</v>
+        <v>136179850</v>
       </c>
       <c r="B115" t="n">
         <v>85481</v>
@@ -13478,17 +13515,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440592</v>
+        <v>440611</v>
       </c>
       <c r="R115" t="n">
-        <v>7171082</v>
+        <v>7171084</v>
       </c>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13517,7 +13554,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13527,7 +13564,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13543,24 +13585,24 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227080</t>
+          <t>https://artportalen.se/Sighting/136179850</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>136227081</v>
+        <v>136179852</v>
       </c>
       <c r="B116" t="n">
         <v>85481</v>
@@ -13586,17 +13628,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>440587</v>
+        <v>440592</v>
       </c>
       <c r="R116" t="n">
-        <v>7171083</v>
+        <v>7171068</v>
       </c>
       <c r="S116" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13625,7 +13667,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13635,7 +13677,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13651,24 +13693,24 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227081</t>
+          <t>https://artportalen.se/Sighting/136179852</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>136227083</v>
+        <v>136179854</v>
       </c>
       <c r="B117" t="n">
         <v>85481</v>
@@ -13694,17 +13736,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Styggdalsbäcken, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440572</v>
+        <v>440616</v>
       </c>
       <c r="R117" t="n">
-        <v>7171049</v>
+        <v>7171059</v>
       </c>
       <c r="S117" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13733,7 +13775,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13743,7 +13785,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13759,24 +13801,24 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+          <t>Cajsa Björkén, Erica Hästdahl, Alexander Singer, Rashid Kadhim, Moa Björnberg Dillner, Uno Skog</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227083</t>
+          <t>https://artportalen.se/Sighting/136179854</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>136227085</v>
+        <v>136202366</v>
       </c>
       <c r="B118" t="n">
         <v>85481</v>
@@ -13806,13 +13848,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440576</v>
+        <v>440594</v>
       </c>
       <c r="R118" t="n">
-        <v>7171059</v>
+        <v>7171053</v>
       </c>
       <c r="S118" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13836,22 +13878,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13860,31 +13892,35 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
+      <c r="AR118" t="inlineStr"/>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136227085</t>
+          <t>https://artportalen.se/Sighting/136202366</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>136227088</v>
+        <v>136227080</v>
       </c>
       <c r="B119" t="n">
         <v>85481</v>
@@ -13908,22 +13944,19 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Styggdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440549</v>
+        <v>440592</v>
       </c>
       <c r="R119" t="n">
-        <v>7171063</v>
+        <v>7171082</v>
       </c>
       <c r="S119" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13952,7 +13985,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13962,7 +13995,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13988,6 +14021,441 @@
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136227080</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>136227081</v>
+      </c>
+      <c r="B120" t="n">
+        <v>85481</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6331313</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Roselliniella nephromatis</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>440587</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7171083</v>
+      </c>
+      <c r="S120" t="n">
+        <v>18</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136227081</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>136227083</v>
+      </c>
+      <c r="B121" t="n">
+        <v>85481</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6331313</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Roselliniella nephromatis</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>440572</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7171049</v>
+      </c>
+      <c r="S121" t="n">
+        <v>31</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136227083</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>136227085</v>
+      </c>
+      <c r="B122" t="n">
+        <v>85481</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6331313</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Roselliniella nephromatis</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>440576</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7171059</v>
+      </c>
+      <c r="S122" t="n">
+        <v>48</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136227085</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>136227088</v>
+      </c>
+      <c r="B123" t="n">
+        <v>85481</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6331313</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Roselliniella nephromatis</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Styggdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>440549</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7171063</v>
+      </c>
+      <c r="S123" t="n">
+        <v>40</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Cajsa Björkén, Uno Skog, Alexander Singer, Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136227088</t>
         </is>
@@ -14113,6 +14581,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203729</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Uno Skog, Cajsa Björkén, Moa Björnberg Dillner</t>
+          <t>Uno Skog, Moa Björnberg Dillner, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
         <v>136183969</v>
       </c>
       <c r="B16" t="n">
-        <v>89472</v>
+        <v>89474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136198394</v>
       </c>
       <c r="B17" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>136183979</v>
       </c>
       <c r="B19" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>136203732</v>
       </c>
       <c r="B20" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>136183980</v>
       </c>
       <c r="B69" t="n">
-        <v>92455</v>
+        <v>92457</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>135669073</v>
       </c>
       <c r="B75" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135669652</v>
       </c>
       <c r="B76" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>136179870</v>
       </c>
       <c r="B77" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>136240862</v>
       </c>
       <c r="B78" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>136225509</v>
       </c>
       <c r="B80" t="n">
-        <v>87696</v>
+        <v>87698</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>100973</v>
+        <v>100975</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>136183946</v>
       </c>
       <c r="B99" t="n">
-        <v>98416</v>
+        <v>98418</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93791</v>
+        <v>93793</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Uno Skog, Moa Björnberg Dillner, Cajsa Björkén</t>
+          <t>Uno Skog, Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136183952</v>
       </c>
       <c r="B5" t="n">
-        <v>83448</v>
+        <v>83452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136183966</v>
       </c>
       <c r="B6" t="n">
-        <v>83448</v>
+        <v>83452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136183960</v>
       </c>
       <c r="B14" t="n">
-        <v>78835</v>
+        <v>78839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Uno Skog, Cajsa Björkén, Moa Björnberg Dillner</t>
+          <t>Uno Skog, Moa Björnberg Dillner, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
         <v>136183969</v>
       </c>
       <c r="B16" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>136183979</v>
       </c>
       <c r="B19" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>136183942</v>
       </c>
       <c r="B28" t="n">
-        <v>79635</v>
+        <v>79639</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>136183963</v>
       </c>
       <c r="B29" t="n">
-        <v>79635</v>
+        <v>79639</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>136183967</v>
       </c>
       <c r="B30" t="n">
-        <v>79635</v>
+        <v>79639</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>136183971</v>
       </c>
       <c r="B31" t="n">
-        <v>79635</v>
+        <v>79639</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>136183973</v>
       </c>
       <c r="B32" t="n">
-        <v>79635</v>
+        <v>79639</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136183982</v>
       </c>
       <c r="B33" t="n">
-        <v>79635</v>
+        <v>79639</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136183943</v>
       </c>
       <c r="B39" t="n">
-        <v>83468</v>
+        <v>83472</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136183945</v>
       </c>
       <c r="B40" t="n">
-        <v>83468</v>
+        <v>83472</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136183951</v>
       </c>
       <c r="B41" t="n">
-        <v>83468</v>
+        <v>83472</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136183957</v>
       </c>
       <c r="B42" t="n">
-        <v>83468</v>
+        <v>83472</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136183962</v>
       </c>
       <c r="B43" t="n">
-        <v>83468</v>
+        <v>83472</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>136183965</v>
       </c>
       <c r="B44" t="n">
-        <v>83468</v>
+        <v>83472</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>136183980</v>
       </c>
       <c r="B69" t="n">
-        <v>92457</v>
+        <v>92459</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136183970</v>
       </c>
       <c r="B82" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>136183964</v>
       </c>
       <c r="B86" t="n">
-        <v>78834</v>
+        <v>78838</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>100975</v>
+        <v>100981</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>136183946</v>
       </c>
       <c r="B99" t="n">
-        <v>98418</v>
+        <v>98424</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>136227078</v>
       </c>
       <c r="B103" t="n">
-        <v>85402</v>
+        <v>85406</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93793</v>
+        <v>93795</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136183952</v>
       </c>
       <c r="B5" t="n">
-        <v>83452</v>
+        <v>83454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136183966</v>
       </c>
       <c r="B6" t="n">
-        <v>83452</v>
+        <v>83454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136183960</v>
       </c>
       <c r="B14" t="n">
-        <v>78839</v>
+        <v>78841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Uno Skog, Moa Björnberg Dillner, Cajsa Björkén</t>
+          <t>Uno Skog, Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
         <v>136183969</v>
       </c>
       <c r="B16" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>136183979</v>
       </c>
       <c r="B19" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>136183942</v>
       </c>
       <c r="B28" t="n">
-        <v>79639</v>
+        <v>79641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>136183963</v>
       </c>
       <c r="B29" t="n">
-        <v>79639</v>
+        <v>79641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>136183967</v>
       </c>
       <c r="B30" t="n">
-        <v>79639</v>
+        <v>79641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>136183971</v>
       </c>
       <c r="B31" t="n">
-        <v>79639</v>
+        <v>79641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>136183973</v>
       </c>
       <c r="B32" t="n">
-        <v>79639</v>
+        <v>79641</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136183982</v>
       </c>
       <c r="B33" t="n">
-        <v>79639</v>
+        <v>79641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136183943</v>
       </c>
       <c r="B39" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136183945</v>
       </c>
       <c r="B40" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136183951</v>
       </c>
       <c r="B41" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136183957</v>
       </c>
       <c r="B42" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136183962</v>
       </c>
       <c r="B43" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>136183965</v>
       </c>
       <c r="B44" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>136183980</v>
       </c>
       <c r="B69" t="n">
-        <v>92459</v>
+        <v>92461</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136183970</v>
       </c>
       <c r="B82" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>136183964</v>
       </c>
       <c r="B86" t="n">
-        <v>78838</v>
+        <v>78840</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>100981</v>
+        <v>100983</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>136183946</v>
       </c>
       <c r="B99" t="n">
-        <v>98424</v>
+        <v>98426</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136183954</v>
       </c>
       <c r="B100" t="n">
-        <v>78479</v>
+        <v>78481</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>136183953</v>
       </c>
       <c r="B101" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>136183974</v>
       </c>
       <c r="B102" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>136227078</v>
       </c>
       <c r="B103" t="n">
-        <v>85406</v>
+        <v>85408</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93795</v>
+        <v>93797</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136183952</v>
       </c>
       <c r="B5" t="n">
-        <v>83454</v>
+        <v>83455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136183966</v>
       </c>
       <c r="B6" t="n">
-        <v>83454</v>
+        <v>83455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136183960</v>
       </c>
       <c r="B14" t="n">
-        <v>78841</v>
+        <v>78842</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>136183969</v>
       </c>
       <c r="B16" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>136183979</v>
       </c>
       <c r="B19" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>136183942</v>
       </c>
       <c r="B28" t="n">
-        <v>79641</v>
+        <v>79642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>136183963</v>
       </c>
       <c r="B29" t="n">
-        <v>79641</v>
+        <v>79642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>136183967</v>
       </c>
       <c r="B30" t="n">
-        <v>79641</v>
+        <v>79642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>136183971</v>
       </c>
       <c r="B31" t="n">
-        <v>79641</v>
+        <v>79642</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>136183973</v>
       </c>
       <c r="B32" t="n">
-        <v>79641</v>
+        <v>79642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136183982</v>
       </c>
       <c r="B33" t="n">
-        <v>79641</v>
+        <v>79642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136183943</v>
       </c>
       <c r="B39" t="n">
-        <v>83474</v>
+        <v>83475</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136183945</v>
       </c>
       <c r="B40" t="n">
-        <v>83474</v>
+        <v>83475</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136183951</v>
       </c>
       <c r="B41" t="n">
-        <v>83474</v>
+        <v>83475</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136183957</v>
       </c>
       <c r="B42" t="n">
-        <v>83474</v>
+        <v>83475</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136183962</v>
       </c>
       <c r="B43" t="n">
-        <v>83474</v>
+        <v>83475</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>136183965</v>
       </c>
       <c r="B44" t="n">
-        <v>83474</v>
+        <v>83475</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>136183980</v>
       </c>
       <c r="B69" t="n">
-        <v>92461</v>
+        <v>92462</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136183970</v>
       </c>
       <c r="B82" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>136183964</v>
       </c>
       <c r="B86" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>100983</v>
+        <v>100984</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>136183946</v>
       </c>
       <c r="B99" t="n">
-        <v>98426</v>
+        <v>98427</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136183954</v>
       </c>
       <c r="B100" t="n">
-        <v>78481</v>
+        <v>78482</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>136183953</v>
       </c>
       <c r="B101" t="n">
-        <v>78487</v>
+        <v>78488</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>136183974</v>
       </c>
       <c r="B102" t="n">
-        <v>78487</v>
+        <v>78488</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93797</v>
+        <v>93798</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -2267,7 +2267,7 @@
         <v>136183969</v>
       </c>
       <c r="B16" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>136183979</v>
       </c>
       <c r="B19" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>136183980</v>
       </c>
       <c r="B69" t="n">
-        <v>92462</v>
+        <v>92468</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>100984</v>
+        <v>100990</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>136183946</v>
       </c>
       <c r="B99" t="n">
-        <v>98427</v>
+        <v>98433</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93798</v>
+        <v>93804</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136183952</v>
       </c>
       <c r="B5" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136183966</v>
       </c>
       <c r="B6" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136183960</v>
       </c>
       <c r="B14" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>136183969</v>
       </c>
       <c r="B16" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>136183979</v>
       </c>
       <c r="B19" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>136183942</v>
       </c>
       <c r="B28" t="n">
-        <v>79642</v>
+        <v>79644</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>136183963</v>
       </c>
       <c r="B29" t="n">
-        <v>79642</v>
+        <v>79644</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>136183967</v>
       </c>
       <c r="B30" t="n">
-        <v>79642</v>
+        <v>79644</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>136183971</v>
       </c>
       <c r="B31" t="n">
-        <v>79642</v>
+        <v>79644</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>136183973</v>
       </c>
       <c r="B32" t="n">
-        <v>79642</v>
+        <v>79644</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136183982</v>
       </c>
       <c r="B33" t="n">
-        <v>79642</v>
+        <v>79644</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136183943</v>
       </c>
       <c r="B39" t="n">
-        <v>83475</v>
+        <v>83479</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136183945</v>
       </c>
       <c r="B40" t="n">
-        <v>83475</v>
+        <v>83479</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136183951</v>
       </c>
       <c r="B41" t="n">
-        <v>83475</v>
+        <v>83479</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136183957</v>
       </c>
       <c r="B42" t="n">
-        <v>83475</v>
+        <v>83479</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136183962</v>
       </c>
       <c r="B43" t="n">
-        <v>83475</v>
+        <v>83479</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>136183965</v>
       </c>
       <c r="B44" t="n">
-        <v>83475</v>
+        <v>83479</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>136183980</v>
       </c>
       <c r="B69" t="n">
-        <v>92468</v>
+        <v>92472</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136183970</v>
       </c>
       <c r="B82" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>136183964</v>
       </c>
       <c r="B86" t="n">
-        <v>78841</v>
+        <v>78843</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>100990</v>
+        <v>100994</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>136183946</v>
       </c>
       <c r="B99" t="n">
-        <v>98433</v>
+        <v>98437</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136183954</v>
       </c>
       <c r="B100" t="n">
-        <v>78482</v>
+        <v>78484</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>136183953</v>
       </c>
       <c r="B101" t="n">
-        <v>78488</v>
+        <v>78490</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>136183974</v>
       </c>
       <c r="B102" t="n">
-        <v>78488</v>
+        <v>78490</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93804</v>
+        <v>93808</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>100994</v>
+        <v>100996</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>136183946</v>
       </c>
       <c r="B99" t="n">
-        <v>98437</v>
+        <v>98439</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136183952</v>
       </c>
       <c r="B5" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136183966</v>
       </c>
       <c r="B6" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136183960</v>
       </c>
       <c r="B14" t="n">
-        <v>78844</v>
+        <v>78847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>136183969</v>
       </c>
       <c r="B16" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>136183979</v>
       </c>
       <c r="B19" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>136183942</v>
       </c>
       <c r="B28" t="n">
-        <v>79644</v>
+        <v>79647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>136183963</v>
       </c>
       <c r="B29" t="n">
-        <v>79644</v>
+        <v>79647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>136183967</v>
       </c>
       <c r="B30" t="n">
-        <v>79644</v>
+        <v>79647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>136183971</v>
       </c>
       <c r="B31" t="n">
-        <v>79644</v>
+        <v>79647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>136183973</v>
       </c>
       <c r="B32" t="n">
-        <v>79644</v>
+        <v>79647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136183982</v>
       </c>
       <c r="B33" t="n">
-        <v>79644</v>
+        <v>79647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136183943</v>
       </c>
       <c r="B39" t="n">
-        <v>83479</v>
+        <v>83481</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136183945</v>
       </c>
       <c r="B40" t="n">
-        <v>83479</v>
+        <v>83481</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136183951</v>
       </c>
       <c r="B41" t="n">
-        <v>83479</v>
+        <v>83481</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136183957</v>
       </c>
       <c r="B42" t="n">
-        <v>83479</v>
+        <v>83481</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136183962</v>
       </c>
       <c r="B43" t="n">
-        <v>83479</v>
+        <v>83481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>136183965</v>
       </c>
       <c r="B44" t="n">
-        <v>83479</v>
+        <v>83481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>136183980</v>
       </c>
       <c r="B69" t="n">
-        <v>92472</v>
+        <v>92474</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136183970</v>
       </c>
       <c r="B82" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>136183964</v>
       </c>
       <c r="B86" t="n">
-        <v>78843</v>
+        <v>78846</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>100996</v>
+        <v>100998</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>136183946</v>
       </c>
       <c r="B99" t="n">
-        <v>98439</v>
+        <v>98441</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136183954</v>
       </c>
       <c r="B100" t="n">
-        <v>78484</v>
+        <v>78487</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>136183953</v>
       </c>
       <c r="B101" t="n">
-        <v>78490</v>
+        <v>78493</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>136183974</v>
       </c>
       <c r="B102" t="n">
-        <v>78490</v>
+        <v>78493</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93808</v>
+        <v>93810</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136183952</v>
       </c>
       <c r="B5" t="n">
-        <v>83461</v>
+        <v>83474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136183966</v>
       </c>
       <c r="B6" t="n">
-        <v>83461</v>
+        <v>83474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136183960</v>
       </c>
       <c r="B14" t="n">
-        <v>78847</v>
+        <v>78860</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>136183969</v>
       </c>
       <c r="B16" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>136183979</v>
       </c>
       <c r="B19" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>136183942</v>
       </c>
       <c r="B28" t="n">
-        <v>79647</v>
+        <v>79660</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>136183963</v>
       </c>
       <c r="B29" t="n">
-        <v>79647</v>
+        <v>79660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>136183967</v>
       </c>
       <c r="B30" t="n">
-        <v>79647</v>
+        <v>79660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>136183971</v>
       </c>
       <c r="B31" t="n">
-        <v>79647</v>
+        <v>79660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>136183973</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>79660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136183982</v>
       </c>
       <c r="B33" t="n">
-        <v>79647</v>
+        <v>79660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136183943</v>
       </c>
       <c r="B39" t="n">
-        <v>83481</v>
+        <v>83494</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136183945</v>
       </c>
       <c r="B40" t="n">
-        <v>83481</v>
+        <v>83494</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136183951</v>
       </c>
       <c r="B41" t="n">
-        <v>83481</v>
+        <v>83494</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136183957</v>
       </c>
       <c r="B42" t="n">
-        <v>83481</v>
+        <v>83494</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136183962</v>
       </c>
       <c r="B43" t="n">
-        <v>83481</v>
+        <v>83494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>136183965</v>
       </c>
       <c r="B44" t="n">
-        <v>83481</v>
+        <v>83494</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>136183941</v>
       </c>
       <c r="B56" t="n">
-        <v>75559</v>
+        <v>75572</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136183950</v>
       </c>
       <c r="B57" t="n">
-        <v>75559</v>
+        <v>75572</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>136183961</v>
       </c>
       <c r="B58" t="n">
-        <v>75559</v>
+        <v>75572</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>136183972</v>
       </c>
       <c r="B59" t="n">
-        <v>75559</v>
+        <v>75572</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>136183977</v>
       </c>
       <c r="B60" t="n">
-        <v>75559</v>
+        <v>75572</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>136183980</v>
       </c>
       <c r="B69" t="n">
-        <v>92474</v>
+        <v>92487</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136183970</v>
       </c>
       <c r="B82" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>136183964</v>
       </c>
       <c r="B86" t="n">
-        <v>78846</v>
+        <v>78859</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>136183976</v>
       </c>
       <c r="B94" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>136183983</v>
       </c>
       <c r="B96" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>100998</v>
+        <v>101011</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>136183946</v>
       </c>
       <c r="B99" t="n">
-        <v>98441</v>
+        <v>98454</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136183954</v>
       </c>
       <c r="B100" t="n">
-        <v>78487</v>
+        <v>78500</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>136183953</v>
       </c>
       <c r="B101" t="n">
-        <v>78493</v>
+        <v>78506</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>136183974</v>
       </c>
       <c r="B102" t="n">
-        <v>78493</v>
+        <v>78506</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>136183956</v>
       </c>
       <c r="B109" t="n">
-        <v>75490</v>
+        <v>75503</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93810</v>
+        <v>93823</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136183952</v>
       </c>
       <c r="B5" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136183966</v>
       </c>
       <c r="B6" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136183960</v>
       </c>
       <c r="B14" t="n">
-        <v>78860</v>
+        <v>78862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>136183969</v>
       </c>
       <c r="B16" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>136183979</v>
       </c>
       <c r="B19" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>136183942</v>
       </c>
       <c r="B28" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>136183963</v>
       </c>
       <c r="B29" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>136183967</v>
       </c>
       <c r="B30" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>136183971</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>136183973</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>136183982</v>
       </c>
       <c r="B33" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136183943</v>
       </c>
       <c r="B39" t="n">
-        <v>83494</v>
+        <v>83496</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136183945</v>
       </c>
       <c r="B40" t="n">
-        <v>83494</v>
+        <v>83496</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136183951</v>
       </c>
       <c r="B41" t="n">
-        <v>83494</v>
+        <v>83496</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136183957</v>
       </c>
       <c r="B42" t="n">
-        <v>83494</v>
+        <v>83496</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136183962</v>
       </c>
       <c r="B43" t="n">
-        <v>83494</v>
+        <v>83496</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>136183965</v>
       </c>
       <c r="B44" t="n">
-        <v>83494</v>
+        <v>83496</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>136183941</v>
       </c>
       <c r="B56" t="n">
-        <v>75572</v>
+        <v>75574</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136183950</v>
       </c>
       <c r="B57" t="n">
-        <v>75572</v>
+        <v>75574</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>136183961</v>
       </c>
       <c r="B58" t="n">
-        <v>75572</v>
+        <v>75574</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>136183972</v>
       </c>
       <c r="B59" t="n">
-        <v>75572</v>
+        <v>75574</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>136183977</v>
       </c>
       <c r="B60" t="n">
-        <v>75572</v>
+        <v>75574</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>136183980</v>
       </c>
       <c r="B69" t="n">
-        <v>92487</v>
+        <v>92489</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136183970</v>
       </c>
       <c r="B82" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>136183964</v>
       </c>
       <c r="B86" t="n">
-        <v>78859</v>
+        <v>78861</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>136183976</v>
       </c>
       <c r="B94" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>136183983</v>
       </c>
       <c r="B96" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>101011</v>
+        <v>101013</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>136183946</v>
       </c>
       <c r="B99" t="n">
-        <v>98454</v>
+        <v>98456</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136183954</v>
       </c>
       <c r="B100" t="n">
-        <v>78500</v>
+        <v>78502</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>136183953</v>
       </c>
       <c r="B101" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>136183974</v>
       </c>
       <c r="B102" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>136183956</v>
       </c>
       <c r="B109" t="n">
-        <v>75503</v>
+        <v>75505</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93823</v>
+        <v>93825</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136183952</v>
       </c>
       <c r="B5" t="n">
-        <v>83476</v>
+        <v>83479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136183966</v>
       </c>
       <c r="B6" t="n">
-        <v>83476</v>
+        <v>83479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136183943</v>
       </c>
       <c r="B39" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136183945</v>
       </c>
       <c r="B40" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136183951</v>
       </c>
       <c r="B41" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136183957</v>
       </c>
       <c r="B42" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136183962</v>
       </c>
       <c r="B43" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>136183965</v>
       </c>
       <c r="B44" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>101013</v>
+        <v>101016</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93825</v>
+        <v>93828</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136183952</v>
       </c>
       <c r="B5" t="n">
-        <v>83479</v>
+        <v>83489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136183966</v>
       </c>
       <c r="B6" t="n">
-        <v>83479</v>
+        <v>83489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136183960</v>
       </c>
       <c r="B14" t="n">
-        <v>78862</v>
+        <v>78872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>136183942</v>
       </c>
       <c r="B28" t="n">
-        <v>79662</v>
+        <v>79672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>136183963</v>
       </c>
       <c r="B29" t="n">
-        <v>79662</v>
+        <v>79672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>136183967</v>
       </c>
       <c r="B30" t="n">
-        <v>79662</v>
+        <v>79672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>136183971</v>
       </c>
       <c r="B31" t="n">
-        <v>79662</v>
+        <v>79672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>136183973</v>
       </c>
       <c r="B32" t="n">
-        <v>79662</v>
+        <v>79672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136183943</v>
       </c>
       <c r="B39" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136183945</v>
       </c>
       <c r="B40" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136183951</v>
       </c>
       <c r="B41" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136183957</v>
       </c>
       <c r="B42" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136183962</v>
       </c>
       <c r="B43" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>136183965</v>
       </c>
       <c r="B44" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>136183941</v>
       </c>
       <c r="B56" t="n">
-        <v>75574</v>
+        <v>75584</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136183950</v>
       </c>
       <c r="B57" t="n">
-        <v>75574</v>
+        <v>75584</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>136183961</v>
       </c>
       <c r="B58" t="n">
-        <v>75574</v>
+        <v>75584</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>136183972</v>
       </c>
       <c r="B59" t="n">
-        <v>75574</v>
+        <v>75584</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>136183977</v>
       </c>
       <c r="B60" t="n">
-        <v>75574</v>
+        <v>75584</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136183970</v>
       </c>
       <c r="B82" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>136183964</v>
       </c>
       <c r="B86" t="n">
-        <v>78861</v>
+        <v>78871</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>101016</v>
+        <v>101026</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136183954</v>
       </c>
       <c r="B100" t="n">
-        <v>78502</v>
+        <v>78512</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>136183953</v>
       </c>
       <c r="B101" t="n">
-        <v>78508</v>
+        <v>78518</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>136183956</v>
       </c>
       <c r="B109" t="n">
-        <v>75505</v>
+        <v>75515</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93828</v>
+        <v>93838</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -11472,7 +11472,7 @@
         <v>136183958</v>
       </c>
       <c r="B97" t="n">
-        <v>101026</v>
+        <v>101027</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93838</v>
+        <v>93839</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136183952</v>
       </c>
       <c r="B5" t="n">
-        <v>83489</v>
+        <v>83492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136183966</v>
       </c>
       <c r="B6" t="n">
-        <v>83489</v>
+        <v>83492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136183960</v>
       </c>
       <c r="B14" t="n">
-        <v>78872</v>
+        <v>78875</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>136183942</v>
       </c>
       <c r="B28" t="n">
-        <v>79672</v>
+        <v>79675</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>136183963</v>
       </c>
       <c r="B29" t="n">
-        <v>79672</v>
+        <v>79675</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>136183967</v>
       </c>
       <c r="B30" t="n">
-        <v>79672</v>
+        <v>79675</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>136183971</v>
       </c>
       <c r="B31" t="n">
-        <v>79672</v>
+        <v>79675</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>136183973</v>
       </c>
       <c r="B32" t="n">
-        <v>79672</v>
+        <v>79675</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136183943</v>
       </c>
       <c r="B39" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136183945</v>
       </c>
       <c r="B40" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136183951</v>
       </c>
       <c r="B41" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136183962</v>
       </c>
       <c r="B43" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>136183965</v>
       </c>
       <c r="B44" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>136183941</v>
       </c>
       <c r="B56" t="n">
-        <v>75584</v>
+        <v>75587</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136183950</v>
       </c>
       <c r="B57" t="n">
-        <v>75584</v>
+        <v>75587</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>136183961</v>
       </c>
       <c r="B58" t="n">
-        <v>75584</v>
+        <v>75587</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>136183972</v>
       </c>
       <c r="B59" t="n">
-        <v>75584</v>
+        <v>75587</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>136183977</v>
       </c>
       <c r="B60" t="n">
-        <v>75584</v>
+        <v>75587</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>136183964</v>
       </c>
       <c r="B86" t="n">
-        <v>78871</v>
+        <v>78874</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>136183954</v>
       </c>
       <c r="B100" t="n">
-        <v>78512</v>
+        <v>78515</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>136183953</v>
       </c>
       <c r="B101" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93839</v>
+        <v>93844</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 71219-2021 artfynd.xlsx
+++ b/artfynd/A 71219-2021 artfynd.xlsx
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Uno Skog, Cajsa Björkén, Moa Björnberg Dillner</t>
+          <t>Uno Skog, Moa Björnberg Dillner, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -16879,7 +16879,7 @@
         <v>136183959</v>
       </c>
       <c r="B145" t="n">
-        <v>93844</v>
+        <v>93846</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
